--- a/artfynd/S 126-2026 artfynd.xlsx
+++ b/artfynd/S 126-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99098</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131872</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/184159</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/211361</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/211362</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/263028</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/243089</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96620</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101584</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/256884</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1893,6 +1948,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/256885</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/744908</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,6 +2180,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1881459</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2226,6 +2296,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1881460</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2337,6 +2412,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1881461</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2448,6 +2528,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1881462</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2559,6 +2644,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1881463</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2670,6 +2760,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1881464</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2781,6 +2876,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1881465</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2892,6 +2992,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1881466</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3003,6 +3108,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1881467</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3114,6 +3224,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1881468</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3225,6 +3340,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1881469</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3336,6 +3456,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1881472</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3447,6 +3572,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2111530</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3558,6 +3688,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2111531</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3669,6 +3804,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2111532</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3780,6 +3920,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2111533</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3891,6 +4036,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2111534</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4002,6 +4152,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2451105</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4113,6 +4268,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1866987</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4224,6 +4384,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2080618</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4330,6 +4495,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98896546</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4440,6 +4610,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83084842</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4550,6 +4725,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83084844</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4660,6 +4840,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83084884</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4770,6 +4955,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83084887</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4880,6 +5070,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83084889</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4990,6 +5185,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83084894</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5096,6 +5296,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98896341</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5202,6 +5407,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98896372</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5308,6 +5518,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98896524</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5414,6 +5629,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98896529</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5520,6 +5740,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98896530</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5626,6 +5851,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98896538</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5732,6 +5962,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98896539</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5838,6 +6073,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98896540</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5944,6 +6184,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98896541</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6050,6 +6295,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98896542</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6156,6 +6406,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98896544</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6262,6 +6517,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98896547</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6368,6 +6628,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98896558</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6474,6 +6739,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98896560</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6580,8 +6850,69 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98896564</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>